--- a/hj/intergrated_test_tool/data/neimeng/监测设备信息.xlsx
+++ b/hj/intergrated_test_tool/data/neimeng/监测设备信息.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\python\script_tools\data\neimeng\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\git\tool\hj\intergrated_test_tool\data\neimeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A67B43-158F-468D-BDD2-72D2261312DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F46C19-A929-4E89-B877-B9BA551D361B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
   <si>
     <t>监测站名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,25 +47,164 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>15250001142004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>锡林郭勒盟东乌旗站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EB500-Em</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>b50c8022-da0a-4ac5-8be2-bb38834f5c66</t>
-  </si>
-  <si>
-    <t>EB500</t>
-  </si>
-  <si>
-    <t>b0aaddda-cca1-4ed0-bc1b-af776300b0f5</t>
+    <t>锡林格勒盟镶黄旗机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌兰察布市罗家村联通站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄂尔多斯机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿拉善盟额济纳旗机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴彦淖尔机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿拉善盟阿右旗机场站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15250001122010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15260001122006</t>
+  </si>
+  <si>
+    <t>15060001122003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15290001120010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15280001122010</t>
+  </si>
+  <si>
+    <t>15290001122002</t>
+  </si>
+  <si>
+    <t>DGR2103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84ed41a7-9e92-4763-8de8-b259ce3724d9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGR2037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3c14574e-9979-4f41-8f56-63e59bad6c1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>db7c689b-6b1f-4495-8b4b-e9b0ecdbd6a8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGR2203</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12c07bbf-d3f9-4f52-9c1c-00505a59ae0d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DGR2034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3bce3873-8066-43cc-9247-3112650e5fc1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5fbfd9fe-2534-4068-8565-ead426e4b783</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>788bc999-c869-420f-b9e2-8aae3657f77d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0e6234e7-0bf8-4562-b0d3-9da3df0448c4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>236a6c45-f7df-47e2-b439-2122369f2aee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>98f54a19-1c81-4261-aa9d-3d83b9c2569c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4eb45094-c7b3-404d-b666-8dc662eb8b59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>f31bf81f-03ae-436a-863d-094ab65d212e</t>
+  </si>
+  <si>
+    <t>EM</t>
+  </si>
+  <si>
+    <t>1b3b9194-003d-446f-8458-7346e13b92c1</t>
+  </si>
+  <si>
+    <t>020a4cb5-da9c-4a36-b06d-2270c0f39cac</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bf7004cd-1fdf-40a3-9ca2-73c04d53c398</t>
+  </si>
+  <si>
+    <t>7872a184-42e3-4b2d-a390-8f1a87e5eaaa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9ded4c3f-d675-4a69-a8a7-92ab035d3481</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bf3a3747-37a5-4f7a-b915-74d674075685</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5985ec7c-622c-464f-b0f1-4e80288868c4</t>
+  </si>
+  <si>
+    <t>bf631d9c-8430-41b4-a779-bb3d94c15468</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>96b0dd8b-2e01-4094-b394-c3fa357c1b85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>e8844261-d788-487f-927d-239c6bb02496</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100a9c24-7a49-4145-bf24-cd8bd8cc2925</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>488d0250-f6d1-4814-9f22-686b3e469ce7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -391,17 +530,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.4140625" customWidth="1"/>
+    <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -418,38 +557,412 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="E2">
+      <c r="B14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
-        <v>1</v>
+      <c r="B22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/hj/intergrated_test_tool/data/neimeng/监测设备信息.xlsx
+++ b/hj/intergrated_test_tool/data/neimeng/监测设备信息.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20392"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\git\tool\hj\intergrated_test_tool\data\neimeng\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F46C19-A929-4E89-B877-B9BA551D361B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0AF056-5E1B-4436-8216-6FC60D999D99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>监测站名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,164 +47,150 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>锡林格勒盟镶黄旗机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌兰察布市罗家村联通站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鄂尔多斯机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿拉善盟额济纳旗机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>巴彦淖尔机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿拉善盟阿右旗机场站</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15250001122010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15260001122006</t>
-  </si>
-  <si>
-    <t>15060001122003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15290001120010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>15280001122010</t>
-  </si>
-  <si>
-    <t>15290001122002</t>
-  </si>
-  <si>
-    <t>DGR2103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>84ed41a7-9e92-4763-8de8-b259ce3724d9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DGR2037</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3c14574e-9979-4f41-8f56-63e59bad6c1c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>db7c689b-6b1f-4495-8b4b-e9b0ecdbd6a8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DGR2203</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>12c07bbf-d3f9-4f52-9c1c-00505a59ae0d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DGR2034</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3bce3873-8066-43cc-9247-3112650e5fc1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5fbfd9fe-2534-4068-8565-ead426e4b783</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>788bc999-c869-420f-b9e2-8aae3657f77d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0e6234e7-0bf8-4562-b0d3-9da3df0448c4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>236a6c45-f7df-47e2-b439-2122369f2aee</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>98f54a19-1c81-4261-aa9d-3d83b9c2569c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4eb45094-c7b3-404d-b666-8dc662eb8b59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>f31bf81f-03ae-436a-863d-094ab65d212e</t>
-  </si>
-  <si>
-    <t>EM</t>
-  </si>
-  <si>
-    <t>1b3b9194-003d-446f-8458-7346e13b92c1</t>
-  </si>
-  <si>
-    <t>020a4cb5-da9c-4a36-b06d-2270c0f39cac</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bf7004cd-1fdf-40a3-9ca2-73c04d53c398</t>
-  </si>
-  <si>
-    <t>7872a184-42e3-4b2d-a390-8f1a87e5eaaa</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>9ded4c3f-d675-4a69-a8a7-92ab035d3481</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bf3a3747-37a5-4f7a-b915-74d674075685</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5985ec7c-622c-464f-b0f1-4e80288868c4</t>
-  </si>
-  <si>
-    <t>bf631d9c-8430-41b4-a779-bb3d94c15468</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>96b0dd8b-2e01-4094-b394-c3fa357c1b85</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>e8844261-d788-487f-927d-239c6bb02496</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100a9c24-7a49-4145-bf24-cd8bd8cc2925</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>488d0250-f6d1-4814-9f22-686b3e469ce7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>包头九原小召湾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15020000130181</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>db899fc7-6046-4124-bec4-68c047135e77</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a6693db1-0639-4a1e-8f51-c26e22673e8d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>083ec6c4-8ed5-467c-8fdf-f7e5317bf139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赤峰机场航空监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15040000130127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4128352d-d2c1-4055-af15-40356a322a82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>974439b6-a3d5-4fce-ad87-761c8daf845a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0998c61d-b3ac-415a-af66-47ebc3b5ccfa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二连浩特机场升级监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15250000130055</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8ac48408-6d1a-4b9a-8983-be9af8d86713</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0efa0031-cbbc-494b-9137-815561d36caa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>de97b473-7dca-401f-8b04-fec01dc89aec</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌海北站监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15030000130056</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8971bab0-a695-45b3-bfa0-c430d9896d24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b9c739cf-182a-4d5c-ae29-49ad787303e7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>锡林浩特机场升级监测站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15250000130050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ac2c0138-1f00-4e9f-8fe6-65d6e276b8d7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65a72de8-1f59-4462-8cfd-6eb2e0bc9e2a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8be218e6-4bb9-427a-9560-0f7e945c2bce</t>
+  </si>
+  <si>
+    <t>阿尔山机场航空站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15220000130165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23aa90fd-a7c0-4fed-908c-1b49a25eb861</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>691b1b84-47e8-4f0b-b77c-062c2e7d1828</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6aa1b69c-a4f0-429e-b4f2-19944fa2fee8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌兰浩特机场航空站</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15220000130170</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b4a6c1e8-115d-402b-b3f2-2d066b0a8244</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6bd9bb12-2c9a-4c67-b96e-1b2664e93b63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>921db4e3-28ee-496e-bc2d-d59c9b5b0701</t>
   </si>
 </sst>
 </file>
@@ -530,12 +516,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.625" customWidth="1"/>
+    <col min="2" max="2" width="21.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
     <col min="4" max="4" width="40.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -559,33 +545,33 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -593,50 +579,50 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -644,16 +630,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -661,16 +647,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -678,33 +664,33 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -712,33 +698,33 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E11">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -746,50 +732,50 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -797,33 +783,33 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -831,138 +817,70 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E21">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
